--- a/Docs/export/current/04_che_do_kinh_te_ai.xlsx
+++ b/Docs/export/current/04_che_do_kinh_te_ai.xlsx
@@ -21,23 +21,22 @@
     <sheet name="Che_do_tham_chieu" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Nang_hang" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Hom_do" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Trang_bi_hang" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Cua_hang" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Nhiem_vu_ngay" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Skin" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Ban_do_menu" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Meta_bang_hang" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Mo_khoa" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Mo_khoa_chung" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Meta_kinh_te_nguon" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Meta_kinh_te_tran" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Meta_kinh_te" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Cai_dat_mac_dinh" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Mutator_tuan" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Thu_hang" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Thuong" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Meta_tham_chieu" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Hang_so_che_do" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Cua_hang" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Nhiem_vu_ngay" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Skin" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Ban_do_menu" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Meta_bang_hang" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Mo_khoa" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Mo_khoa_chung" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Meta_kinh_te_nguon" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Meta_kinh_te_tran" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Meta_kinh_te" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Cai_dat_mac_dinh" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Mutator_tuan" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Thu_hang" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Thuong" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Meta_tham_chieu" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Hang_so_che_do" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Che_do'!$A$1:$AY$13</definedName>
@@ -54,23 +53,22 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Che_do_tham_chieu'!$A$1:$V$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Nang_hang'!$A$1:$F$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Hom_do'!$A$1:$R$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Trang_bi_hang'!$A$1:$K$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Cua_hang'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Nhiem_vu_ngay'!$A$1:$F$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Skin'!$A$1:$K$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Ban_do_menu'!$A$1:$F$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Meta_bang_hang'!$A$1:$F$113</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Mo_khoa'!$A$1:$G$89</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Mo_khoa_chung'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Meta_kinh_te_nguon'!$A$1:$I$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Meta_kinh_te_tran'!$A$1:$J$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Meta_kinh_te'!$A$1:$K$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'Cai_dat_mac_dinh'!$A$1:$E$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Mutator_tuan'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Thu_hang'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Thuong'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'Meta_tham_chieu'!$A$1:$U$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'Hang_so_che_do'!$A$1:$K$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Cua_hang'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Nhiem_vu_ngay'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Skin'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Ban_do_menu'!$A$1:$F$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Meta_bang_hang'!$A$1:$F$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Mo_khoa'!$A$1:$G$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Mo_khoa_chung'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Meta_kinh_te_nguon'!$A$1:$I$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Meta_kinh_te_tran'!$A$1:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Meta_kinh_te'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Cai_dat_mac_dinh'!$A$1:$E$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'Mutator_tuan'!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Thu_hang'!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Thuong'!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Meta_tham_chieu'!$A$1:$U$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'Hang_so_che_do'!$A$1:$K$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11622,918 +11620,6 @@
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>bang</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>chi_so</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>gia_tri</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>gia_tri_0</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>gia_tri_1</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>gia_tri_2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>gia_tri_3</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>gia_tri_4</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>nguon</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>raw_json</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Cap/0</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Cap</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:198 (Cap[0])</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cap/1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Cap</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:198 (Cap[1])</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cap/2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Cap</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:198 (Cap[2])</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cap/3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Cap</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:198 (Cap[3])</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cap/4</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cap</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:198 (Cap[4])</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cap/5</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Cap</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:198 (Cap[5])</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GoldGuaranteed/0</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>GoldGuaranteed</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:429 (GoldGuaranteed[0])</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GoldGuaranteed/1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>GoldGuaranteed</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:429 (GoldGuaranteed[1])</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GoldGuaranteed/2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>GoldGuaranteed</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:429 (GoldGuaranteed[2])</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>GoldGuaranteed/3</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>GoldGuaranteed</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:429 (GoldGuaranteed[3])</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>GoldGuaranteed/4</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>GoldGuaranteed</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:429 (GoldGuaranteed[4])</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>LegendaryGuaranteed/0</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>LegendaryGuaranteed</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:430 (LegendaryGuaranteed[0])</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>LegendaryGuaranteed/1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>LegendaryGuaranteed</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:430 (LegendaryGuaranteed[1])</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>LegendaryGuaranteed/2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>LegendaryGuaranteed</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:430 (LegendaryGuaranteed[2])</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>LegendaryGuaranteed/3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>LegendaryGuaranteed</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:430 (LegendaryGuaranteed[3])</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LegendaryGuaranteed/4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>LegendaryGuaranteed</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:430 (LegendaryGuaranteed[4])</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>LevelCap/0</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>LevelCap</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:180 (LevelCap[0])</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>LevelCap/1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>LevelCap</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:180 (LevelCap[1])</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>LevelCap/2</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>LevelCap</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="n">
-        <v>15</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:180 (LevelCap[2])</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>LevelCap/3</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>LevelCap</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" t="n">
-        <v>20</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:180 (LevelCap[3])</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>LevelCap/4</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>LevelCap</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" t="n">
-        <v>25</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:180 (LevelCap[4])</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Top/0</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:185 (Top[0])</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>[0.03,0.05,0.08,0.11,0.14]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Top/1</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:186 (Top[1])</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>[0.03,0.05,0.08,0.11,0.14]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Top/2</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:187 (Top[2])</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>[0.03,0.05,0.08,0.11,0.14]</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Top/3</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:188 (Top[3])</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>[0.03,0.05,0.08,0.11,0.14]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Top/4</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:189 (Top[4])</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>[0.02,0.035,0.05,0.065,0.08]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Top/5</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>5</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:190 (Top[5])</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>[0.002,0.004,0.006,0.008,0.01]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:K28"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
@@ -12760,7 +11846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13054,7 +12140,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13583,7 +12669,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14433,6 +13519,3400 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F26"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>bang</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>chi_so</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>gia_tri</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>nguon</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>raw_json</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#AntiAliasingLevels/0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#AntiAliasingLevels</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:45 (AntiAliasingLevels[0])</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#AntiAliasingLevels/1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#AntiAliasingLevels</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:45 (AntiAliasingLevels[1])</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#AntiAliasingLevels/2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#AntiAliasingLevels</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:45 (AntiAliasingLevels[2])</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#FrameRates/0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#FrameRates</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:46 (FrameRates[0])</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#FrameRates/1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#FrameRates</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:46 (FrameRates[1])</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#FrameRates/2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#FrameRates</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>90</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:46 (FrameRates[2])</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#FrameRates/3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#FrameRates</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>120</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:46 (FrameRates[3])</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#RenderScales/0</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#RenderScales</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>70</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:44 (RenderScales[0])</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#RenderScales/1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#RenderScales</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>85</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:44 (RenderScales[1])</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#RenderScales/2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GraphicsOptions#RenderScales</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:44 (RenderScales[2])</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllSupports/0</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllSupports</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>artillery_barrage</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:153 (AllSupports[0])</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>"artillery_barrage"</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllSupports/1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllSupports</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>airstrike</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:153 (AllSupports[1])</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>"airstrike"</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllSupports/2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllSupports</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>cruise_missile</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:153 (AllSupports[2])</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>"cruise_missile"</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllSupports/3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllSupports</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>repair_drop</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:153 (AllSupports[3])</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>"repair_drop"</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllSupports/4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllSupports</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>napalm_strike</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:153 (AllSupports[4])</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>"napalm_strike"</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllSupports/5</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllSupports</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>remote_mines</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:154 (AllSupports[5])</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>"remote_mines"</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllSupports/6</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllSupports</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>field_tower</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:154 (AllSupports[6])</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>"field_tower"</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllSupports/7</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllSupports</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>glide_bomb_strike</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:156 (AllSupports[7])</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>"glide_bomb_strike"</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>scout_jeep</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:118 (AllVehicles[0])</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>"scout_jeep"</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>armored_car</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:118 (AllVehicles[1])</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>"armored_car"</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>rocket_technical</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:118 (AllVehicles[2])</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>"rocket_technical"</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>light_tank</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:118 (AllVehicles[3])</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>"light_tank"</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/4</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>main_battle_tank</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:118 (AllVehicles[4])</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>"main_battle_tank"</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/5</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>heavy_tank</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:118 (AllVehicles[5])</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>"heavy_tank"</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/6</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>tank_destroyer</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:119 (AllVehicles[6])</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>"tank_destroyer"</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/7</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>flame_tank</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:119 (AllVehicles[7])</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>"flame_tank"</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/8</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>mortar_carrier</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:119 (AllVehicles[8])</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>"mortar_carrier"</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/9</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>9</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>artillery</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:119 (AllVehicles[9])</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>"artillery"</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>mlrs</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:119 (AllVehicles[10])</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>"mlrs"</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>11</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>aa_vehicle</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:119 (AllVehicles[11])</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>"aa_vehicle"</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>12</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>sam_launcher</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:119 (AllVehicles[12])</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>"sam_launcher"</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/13</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>13</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>scout_heli</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:120 (AllVehicles[13])</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>"scout_heli"</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/14</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>14</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>attack_helicopter</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:120 (AllVehicles[14])</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>"attack_helicopter"</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/15</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>15</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>strike_drone</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:120 (AllVehicles[15])</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>"strike_drone"</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>attack_jet</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:120 (AllVehicles[16])</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>"attack_jet"</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/17</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ifv</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:121 (AllVehicles[17])</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>"ifv"</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/18</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>18</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>thermobaric_launcher</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:121 (AllVehicles[18])</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>"thermobaric_launcher"</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/19</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>19</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>heavy_aa</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:121 (AllVehicles[19])</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>"heavy_aa"</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/20</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>20</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>titan_tank</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:121 (AllVehicles[20])</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>"titan_tank"</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/21</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>21</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>heavy_bomber</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:122 (AllVehicles[21])</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>"heavy_bomber"</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/22</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>22</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>stealth_bomber</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:122 (AllVehicles[22])</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>"stealth_bomber"</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/23</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>23</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>sky_gunship</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:124 (AllVehicles[23])</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>"sky_gunship"</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/24</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>24</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>twin_tank</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:125 (AllVehicles[24])</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>"twin_tank"</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>25</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>siege_tank</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:125 (AllVehicles[25])</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>"siege_tank"</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>26</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>heavy_rocket_artillery</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:125 (AllVehicles[26])</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>"heavy_rocket_artillery"</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/27</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>27</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ballistic_launcher</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:125 (AllVehicles[27])</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>"ballistic_launcher"</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/28</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>28</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>engineer_vehicle</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:127 (AllVehicles[28])</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>"engineer_vehicle"</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/29</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>29</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ew_jammer</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:127 (AllVehicles[29])</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>"ew_jammer"</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/30</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>30</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>fpv_carrier</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:127 (AllVehicles[30])</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>"fpv_carrier"</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/31</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>31</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>mine_layer</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:127 (AllVehicles[31])</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>"mine_layer"</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/32</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>32</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ammo_carrier</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:127 (AllVehicles[32])</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>"ammo_carrier"</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/33</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>33</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>fighter_jet</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:128 (AllVehicles[33])</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>"fighter_jet"</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/34</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>34</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>recon_drone</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:128 (AllVehicles[34])</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>"recon_drone"</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/35</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>35</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>vbied</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:129 (AllVehicles[35])</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>"vbied"</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/36</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>36</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>zu23_technical</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:129 (AllVehicles[36])</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>"zu23_technical"</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/37</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>37</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>shahed_truck</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:129 (AllVehicles[37])</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>"shahed_truck"</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/38</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>38</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>iron_beam</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:129 (AllVehicles[38])</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>"iron_beam"</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/39</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>39</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>railgun_truck</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:129 (AllVehicles[39])</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>"railgun_truck"</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/40</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>40</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>command_vehicle</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:130 (AllVehicles[40])</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>"command_vehicle"</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/41</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>41</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>wheeled_gun</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:130 (AllVehicles[41])</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>"wheeled_gun"</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/42</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>42</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>long_sam</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:130 (AllVehicles[42])</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>"long_sam"</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/43</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>43</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>armored_bulldozer</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:131 (AllVehicles[43])</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>"armored_bulldozer"</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/44</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>44</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>stealth_fighter</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:133 (AllVehicles[44])</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>"stealth_fighter"</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/45</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>45</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>laser_tank</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:133 (AllVehicles[45])</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>"laser_tank"</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/46</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>46</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>shield_carrier</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:133 (AllVehicles[46])</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>"shield_carrier"</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/47</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>47</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>swarm_carrier</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:133 (AllVehicles[47])</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>"swarm_carrier"</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/48</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>48</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>aa_gun_vehicle</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:135 (AllVehicles[48])</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>"aa_gun_vehicle"</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/49</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>49</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>recoilless_jeep</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:136 (AllVehicles[49])</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>"recoilless_jeep"</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/50</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>50</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>sp_mortar</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:137 (AllVehicles[50])</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>"sp_mortar"</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/51</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>51</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>next_gen_tank</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:141 (AllVehicles[51])</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>"next_gen_tank"</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/52</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>52</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>demolition_line_vehicle</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:142 (AllVehicles[52])</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>"demolition_line_vehicle"</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/53</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>53</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>river_patrol_boat</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:143 (AllVehicles[53])</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>"river_patrol_boat"</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/54</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>54</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>river_gunboat</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:144 (AllVehicles[54])</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>"river_gunboat"</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/55</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>55</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>stealth_naval_strike</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:145 (AllVehicles[55])</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>"stealth_naval_strike"</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/56</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>56</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>twin_rotor_gunship</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:146 (AllVehicles[56])</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>"twin_rotor_gunship"</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/57</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>57</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ground_cruise_missile_vehicle</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:147 (AllVehicles[57])</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>"ground_cruise_missile_vehicle"</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles/58</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>MatchSettings#AllVehicles</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>58</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>gps_jammer_vehicle</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:148 (AllVehicles[58])</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>"gps_jammer_vehicle"</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultLarge/0</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultLarge</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>heavy_turret</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:191 (DefaultLarge[0])</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>"heavy_turret"</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultLarge/1</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultLarge</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>missile_battery</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:191 (DefaultLarge[1])</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>"missile_battery"</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultMedium/0</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultMedium</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>gun_turret</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:185 (DefaultMedium[0])</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>"gun_turret"</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultMedium/1</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultMedium</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>rocket_turret</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:185 (DefaultMedium[1])</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>"rocket_turret"</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultMedium/2</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultMedium</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>atgm_tower</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:185 (DefaultMedium[2])</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>"atgm_tower"</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultSmall/0</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultSmall</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>guard_tower</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:183 (DefaultSmall[0])</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>"guard_tower"</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultSmall/1</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultSmall</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>aa_turret</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:183 (DefaultSmall[1])</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>"aa_turret"</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultSmall/2</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultSmall</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>mg_bunker</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:183 (DefaultSmall[2])</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>"mg_bunker"</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultSmall/3</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultSmall</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>guard_tower</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:183 (DefaultSmall[3])</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>"guard_tower"</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultSmall/4</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultSmall</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>4</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>aa_turret</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:183 (DefaultSmall[4])</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>"aa_turret"</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultSmall/5</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PlayerProfile#DefaultSmall</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>5</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>mg_bunker</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:183 (DefaultSmall[5])</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>"mg_bunker"</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>PlayerProfile#OldDoctrinesSold/0</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PlayerProfile#OldDoctrinesSold</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:215 (OldDoctrinesSold[0])</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>"air"</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>PlayerProfile#OldDoctrinesSold/1</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PlayerProfile#OldDoctrinesSold</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>artillery</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:215 (OldDoctrinesSold[1])</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>"artillery"</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>PlayerProfile#OldDoctrinesSold/2</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>PlayerProfile#OldDoctrinesSold</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>blitz</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:215 (OldDoctrinesSold[2])</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>"blitz"</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>PlayerProfile#OldDoctrinesSold/3</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>PlayerProfile#OldDoctrinesSold</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:215 (OldDoctrinesSold[3])</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>"logistics"</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Progression#FormerStarters/0</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Progression#FormerStarters</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>light_tank</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:38 (FormerStarters[0])</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>"light_tank"</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Progression#FormerStarters/1</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Progression#FormerStarters</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>aa_vehicle</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:38 (FormerStarters[1])</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>"aa_vehicle"</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Progression#FormerStarters/2</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Progression#FormerStarters</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>artillery</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:38 (FormerStarters[2])</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>"artillery"</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Progression#Items/0</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Progression#Items</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>moab</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:168 (Items[0])</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>"moab"</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Progression#Items/1</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Progression#Items</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>cluster_strike</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:168 (Items[1])</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>"cluster_strike"</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Progression#Items/2</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Progression#Items</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>2</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>field_repair</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:168 (Items[2])</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>"field_repair"</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Progression#Items/3</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Progression#Items</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>3</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>emp_blast</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:168 (Items[3])</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>"emp_blast"</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Progression#Items/4</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Progression#Items</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>4</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>shield_dome</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:168 (Items[4])</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>"shield_dome"</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Progression#SheetLoot/0</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Progression#SheetLoot</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>swarm_carrier</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:41 (SheetLoot[0])</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>"swarm_carrier"</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Progression#SheetLoot/1</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Progression#SheetLoot</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>railgun_truck</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:41 (SheetLoot[1])</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>"railgun_truck"</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Progression#StarterSupports/0</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Progression#StarterSupports</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>artillery_barrage</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:91 (StarterSupports[0])</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>"artillery_barrage"</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Progression#StarterSupports/1</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Progression#StarterSupports</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>repair_drop</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:91 (StarterSupports[1])</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>"repair_drop"</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Progression#StarterTowers/0</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Progression#StarterTowers</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>guard_tower</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:94 (StarterTowers[0])</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>"guard_tower"</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Progression#StarterTowers/1</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Progression#StarterTowers</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>mg_bunker</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:94 (StarterTowers[1])</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>"mg_bunker"</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Progression#StarterTowers/2</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Progression#StarterTowers</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>aa_turret</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:94 (StarterTowers[2])</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>"aa_turret"</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Progression#StarterTowers/3</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Progression#StarterTowers</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>gun_turret</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:94 (StarterTowers[3])</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>"gun_turret"</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Progression#StarterVehicles/0</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Progression#StarterVehicles</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>scout_jeep</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:35 (StarterVehicles[0])</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>"scout_jeep"</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Progression#StarterVehicles/1</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Progression#StarterVehicles</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>armored_car</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:35 (StarterVehicles[1])</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>"armored_car"</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Progression#StarterVehicles/2</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Progression#StarterVehicles</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ifv</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:35 (StarterVehicles[2])</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>"ifv"</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Progression#StarterVehicles/3</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Progression#StarterVehicles</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>3</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>main_battle_tank</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:35 (StarterVehicles[3])</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>"main_battle_tank"</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14928,3400 +17408,6 @@
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>bang</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>chi_so</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>gia_tri</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>nguon</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>raw_json</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#AntiAliasingLevels/0</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#AntiAliasingLevels</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:45 (AntiAliasingLevels[0])</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#AntiAliasingLevels/1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#AntiAliasingLevels</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:45 (AntiAliasingLevels[1])</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#AntiAliasingLevels/2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#AntiAliasingLevels</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:45 (AntiAliasingLevels[2])</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#FrameRates/0</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#FrameRates</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:46 (FrameRates[0])</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#FrameRates/1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#FrameRates</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:46 (FrameRates[1])</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#FrameRates/2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#FrameRates</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>90</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:46 (FrameRates[2])</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#FrameRates/3</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#FrameRates</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>120</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:46 (FrameRates[3])</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#RenderScales/0</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#RenderScales</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>70</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:44 (RenderScales[0])</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#RenderScales/1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#RenderScales</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>85</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:44 (RenderScales[1])</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#RenderScales/2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>GraphicsOptions#RenderScales</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>100</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs:44 (RenderScales[2])</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllSupports/0</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllSupports</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>artillery_barrage</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:153 (AllSupports[0])</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>"artillery_barrage"</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllSupports/1</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllSupports</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>airstrike</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:153 (AllSupports[1])</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>"airstrike"</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllSupports/2</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllSupports</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>cruise_missile</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:153 (AllSupports[2])</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>"cruise_missile"</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllSupports/3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllSupports</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>repair_drop</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:153 (AllSupports[3])</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>"repair_drop"</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllSupports/4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllSupports</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>napalm_strike</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:153 (AllSupports[4])</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>"napalm_strike"</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllSupports/5</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllSupports</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>remote_mines</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:154 (AllSupports[5])</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>"remote_mines"</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllSupports/6</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllSupports</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>6</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>field_tower</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:154 (AllSupports[6])</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>"field_tower"</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllSupports/7</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllSupports</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>7</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>glide_bomb_strike</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:156 (AllSupports[7])</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>"glide_bomb_strike"</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/0</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>scout_jeep</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:118 (AllVehicles[0])</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>"scout_jeep"</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/1</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>armored_car</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:118 (AllVehicles[1])</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>"armored_car"</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/2</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>rocket_technical</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:118 (AllVehicles[2])</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>"rocket_technical"</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/3</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>3</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>light_tank</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:118 (AllVehicles[3])</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>"light_tank"</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/4</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>main_battle_tank</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:118 (AllVehicles[4])</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>"main_battle_tank"</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/5</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>heavy_tank</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:118 (AllVehicles[5])</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>"heavy_tank"</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/6</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>6</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>tank_destroyer</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:119 (AllVehicles[6])</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>"tank_destroyer"</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/7</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>7</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>flame_tank</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:119 (AllVehicles[7])</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>"flame_tank"</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/8</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>8</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>mortar_carrier</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:119 (AllVehicles[8])</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>"mortar_carrier"</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/9</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>9</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>artillery</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:119 (AllVehicles[9])</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>"artillery"</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/10</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>10</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>mlrs</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:119 (AllVehicles[10])</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>"mlrs"</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/11</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>11</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>aa_vehicle</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:119 (AllVehicles[11])</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>"aa_vehicle"</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/12</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>12</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>sam_launcher</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:119 (AllVehicles[12])</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>"sam_launcher"</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/13</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>13</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>scout_heli</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:120 (AllVehicles[13])</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>"scout_heli"</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/14</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>14</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>attack_helicopter</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:120 (AllVehicles[14])</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>"attack_helicopter"</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/15</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>15</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>strike_drone</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:120 (AllVehicles[15])</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>"strike_drone"</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/16</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>16</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>attack_jet</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:120 (AllVehicles[16])</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>"attack_jet"</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/17</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>17</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>ifv</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:121 (AllVehicles[17])</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>"ifv"</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/18</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>18</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>thermobaric_launcher</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:121 (AllVehicles[18])</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>"thermobaric_launcher"</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/19</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>19</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>heavy_aa</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:121 (AllVehicles[19])</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>"heavy_aa"</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/20</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>20</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>titan_tank</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:121 (AllVehicles[20])</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>"titan_tank"</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/21</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>21</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>heavy_bomber</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:122 (AllVehicles[21])</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>"heavy_bomber"</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/22</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>22</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>stealth_bomber</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:122 (AllVehicles[22])</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>"stealth_bomber"</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/23</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>23</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>sky_gunship</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:124 (AllVehicles[23])</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>"sky_gunship"</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/24</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>24</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>twin_tank</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:125 (AllVehicles[24])</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>"twin_tank"</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/25</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>25</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>siege_tank</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:125 (AllVehicles[25])</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>"siege_tank"</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/26</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>26</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>heavy_rocket_artillery</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:125 (AllVehicles[26])</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>"heavy_rocket_artillery"</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/27</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>27</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>ballistic_launcher</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:125 (AllVehicles[27])</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>"ballistic_launcher"</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/28</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>28</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>engineer_vehicle</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:127 (AllVehicles[28])</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>"engineer_vehicle"</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/29</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>29</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>ew_jammer</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:127 (AllVehicles[29])</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>"ew_jammer"</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/30</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>30</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>fpv_carrier</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:127 (AllVehicles[30])</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>"fpv_carrier"</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/31</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>31</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>mine_layer</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:127 (AllVehicles[31])</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>"mine_layer"</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/32</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>32</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>ammo_carrier</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:127 (AllVehicles[32])</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>"ammo_carrier"</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/33</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>33</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>fighter_jet</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:128 (AllVehicles[33])</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>"fighter_jet"</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/34</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>34</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>recon_drone</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:128 (AllVehicles[34])</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>"recon_drone"</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/35</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>35</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>vbied</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:129 (AllVehicles[35])</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>"vbied"</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/36</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>36</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>zu23_technical</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:129 (AllVehicles[36])</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>"zu23_technical"</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/37</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>37</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>shahed_truck</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:129 (AllVehicles[37])</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>"shahed_truck"</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/38</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>38</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>iron_beam</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:129 (AllVehicles[38])</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>"iron_beam"</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/39</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>39</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>railgun_truck</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:129 (AllVehicles[39])</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>"railgun_truck"</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/40</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>40</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>command_vehicle</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:130 (AllVehicles[40])</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>"command_vehicle"</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/41</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>41</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>wheeled_gun</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:130 (AllVehicles[41])</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>"wheeled_gun"</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/42</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>42</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>long_sam</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:130 (AllVehicles[42])</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>"long_sam"</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/43</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>43</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>armored_bulldozer</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:131 (AllVehicles[43])</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>"armored_bulldozer"</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/44</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>44</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>stealth_fighter</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:133 (AllVehicles[44])</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>"stealth_fighter"</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/45</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>45</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>laser_tank</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:133 (AllVehicles[45])</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>"laser_tank"</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/46</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>46</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>shield_carrier</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:133 (AllVehicles[46])</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>"shield_carrier"</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/47</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>47</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>swarm_carrier</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:133 (AllVehicles[47])</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>"swarm_carrier"</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/48</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>48</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>aa_gun_vehicle</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:135 (AllVehicles[48])</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>"aa_gun_vehicle"</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/49</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>49</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>recoilless_jeep</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:136 (AllVehicles[49])</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>"recoilless_jeep"</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/50</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>50</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>sp_mortar</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:137 (AllVehicles[50])</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>"sp_mortar"</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/51</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>51</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>next_gen_tank</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:141 (AllVehicles[51])</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>"next_gen_tank"</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/52</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>52</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>demolition_line_vehicle</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:142 (AllVehicles[52])</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>"demolition_line_vehicle"</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/53</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>53</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>river_patrol_boat</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:143 (AllVehicles[53])</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>"river_patrol_boat"</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/54</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>54</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>river_gunboat</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:144 (AllVehicles[54])</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>"river_gunboat"</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/55</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>55</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>stealth_naval_strike</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:145 (AllVehicles[55])</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>"stealth_naval_strike"</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/56</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>56</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>twin_rotor_gunship</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:146 (AllVehicles[56])</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>"twin_rotor_gunship"</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/57</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>57</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>ground_cruise_missile_vehicle</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:147 (AllVehicles[57])</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>"ground_cruise_missile_vehicle"</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles/58</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>MatchSettings#AllVehicles</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>58</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>gps_jammer_vehicle</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/MatchSettings.cs:148 (AllVehicles[58])</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>"gps_jammer_vehicle"</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultLarge/0</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultLarge</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>heavy_turret</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:191 (DefaultLarge[0])</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>"heavy_turret"</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultLarge/1</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultLarge</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>missile_battery</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:191 (DefaultLarge[1])</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>"missile_battery"</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultMedium/0</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultMedium</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>gun_turret</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:185 (DefaultMedium[0])</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>"gun_turret"</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultMedium/1</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultMedium</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>rocket_turret</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:185 (DefaultMedium[1])</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>"rocket_turret"</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultMedium/2</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultMedium</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>2</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>atgm_tower</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:185 (DefaultMedium[2])</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>"atgm_tower"</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultSmall/0</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultSmall</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>guard_tower</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:183 (DefaultSmall[0])</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>"guard_tower"</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultSmall/1</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultSmall</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>aa_turret</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:183 (DefaultSmall[1])</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>"aa_turret"</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultSmall/2</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultSmall</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>2</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>mg_bunker</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:183 (DefaultSmall[2])</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>"mg_bunker"</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultSmall/3</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultSmall</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>3</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>guard_tower</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:183 (DefaultSmall[3])</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>"guard_tower"</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultSmall/4</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultSmall</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>4</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>aa_turret</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:183 (DefaultSmall[4])</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>"aa_turret"</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultSmall/5</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>PlayerProfile#DefaultSmall</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>5</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>mg_bunker</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:183 (DefaultSmall[5])</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>"mg_bunker"</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>PlayerProfile#OldDoctrinesSold/0</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>PlayerProfile#OldDoctrinesSold</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>air</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:215 (OldDoctrinesSold[0])</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>"air"</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>PlayerProfile#OldDoctrinesSold/1</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>PlayerProfile#OldDoctrinesSold</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>1</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>artillery</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:215 (OldDoctrinesSold[1])</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>"artillery"</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>PlayerProfile#OldDoctrinesSold/2</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>PlayerProfile#OldDoctrinesSold</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>2</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>blitz</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:215 (OldDoctrinesSold[2])</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>"blitz"</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>PlayerProfile#OldDoctrinesSold/3</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>PlayerProfile#OldDoctrinesSold</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>3</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>logistics</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/PlayerProfile.cs:215 (OldDoctrinesSold[3])</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>"logistics"</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Progression#FormerStarters/0</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Progression#FormerStarters</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>light_tank</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:38 (FormerStarters[0])</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>"light_tank"</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Progression#FormerStarters/1</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Progression#FormerStarters</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>aa_vehicle</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:38 (FormerStarters[1])</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>"aa_vehicle"</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Progression#FormerStarters/2</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Progression#FormerStarters</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>2</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>artillery</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:38 (FormerStarters[2])</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>"artillery"</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Progression#Items/0</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Progression#Items</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>moab</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:168 (Items[0])</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>"moab"</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Progression#Items/1</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Progression#Items</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>cluster_strike</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:168 (Items[1])</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>"cluster_strike"</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Progression#Items/2</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Progression#Items</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>2</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>field_repair</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:168 (Items[2])</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>"field_repair"</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Progression#Items/3</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Progression#Items</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>3</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>emp_blast</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:168 (Items[3])</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>"emp_blast"</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Progression#Items/4</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Progression#Items</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>4</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>shield_dome</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:168 (Items[4])</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>"shield_dome"</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Progression#SheetLoot/0</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Progression#SheetLoot</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>swarm_carrier</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:41 (SheetLoot[0])</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>"swarm_carrier"</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Progression#SheetLoot/1</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Progression#SheetLoot</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>1</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>railgun_truck</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:41 (SheetLoot[1])</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>"railgun_truck"</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Progression#StarterSupports/0</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Progression#StarterSupports</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>artillery_barrage</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:91 (StarterSupports[0])</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>"artillery_barrage"</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Progression#StarterSupports/1</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Progression#StarterSupports</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>1</v>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>repair_drop</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:91 (StarterSupports[1])</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>"repair_drop"</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Progression#StarterTowers/0</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Progression#StarterTowers</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>guard_tower</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:94 (StarterTowers[0])</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>"guard_tower"</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Progression#StarterTowers/1</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Progression#StarterTowers</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>1</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>mg_bunker</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:94 (StarterTowers[1])</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>"mg_bunker"</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Progression#StarterTowers/2</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Progression#StarterTowers</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>2</v>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>aa_turret</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:94 (StarterTowers[2])</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>"aa_turret"</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Progression#StarterTowers/3</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Progression#StarterTowers</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>3</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>gun_turret</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:94 (StarterTowers[3])</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>"gun_turret"</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Progression#StarterVehicles/0</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Progression#StarterVehicles</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>scout_jeep</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:35 (StarterVehicles[0])</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>"scout_jeep"</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Progression#StarterVehicles/1</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Progression#StarterVehicles</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>1</v>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>armored_car</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:35 (StarterVehicles[1])</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>"armored_car"</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Progression#StarterVehicles/2</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Progression#StarterVehicles</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>2</v>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>ifv</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:35 (StarterVehicles[2])</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>"ifv"</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Progression#StarterVehicles/3</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Progression#StarterVehicles</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>3</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>main_battle_tank</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Progression.cs:35 (StarterVehicles[3])</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>"main_battle_tank"</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F113"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
@@ -20578,7 +19664,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20731,7 +19817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21680,7 +20766,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22226,7 +21312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22720,7 +21806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23238,7 +22324,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23309,7 +22395,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23380,7 +22466,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23451,205 +22537,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>thu_tu_xep_hang</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>he_so_tang_thuong</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>nguon</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>raw_json</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>bossrush</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>-bosses;+seconds;-parts</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: matchRules.leaderboards.bossrush</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>["-bosses","+seconds","-parts"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>bossrushEndless</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>-bosses;+seconds;-parts</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: matchRules.leaderboards.bossrushEndless</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>["-bosses","+seconds","-parts"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>defendEndless</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>-waves;-killedBaseCp;-seconds</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: matchRules.leaderboards.defendEndless</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>["-waves","-killedBaseCp","-seconds"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>endless</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>-waves;-killedBaseCp;-seconds</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: matchRules.leaderboards.endless</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>["-waves","-killedBaseCp","-seconds"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>survivalEndless</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>-waves;-killedBaseCp;-seconds</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: matchRules.leaderboards.survivalEndless</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>["-waves","-killedBaseCp","-seconds"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>-cleared;+attempts;+seconds</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: matchRules.leaderboards.weekly</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>["-cleared","+attempts","+seconds"]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E7"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24612,7 +23500,205 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>thu_tu_xep_hang</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>he_so_tang_thuong</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nguon</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>raw_json</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bossrush</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>-bosses;+seconds;-parts</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: matchRules.leaderboards.bossrush</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>["-bosses","+seconds","-parts"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bossrushEndless</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-bosses;+seconds;-parts</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: matchRules.leaderboards.bossrushEndless</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>["-bosses","+seconds","-parts"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>defendEndless</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-waves;-killedBaseCp;-seconds</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: matchRules.leaderboards.defendEndless</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>["-waves","-killedBaseCp","-seconds"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>endless</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-waves;-killedBaseCp;-seconds</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: matchRules.leaderboards.endless</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>["-waves","-killedBaseCp","-seconds"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>survivalEndless</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-waves;-killedBaseCp;-seconds</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: matchRules.leaderboards.survivalEndless</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>["-waves","-killedBaseCp","-seconds"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-cleared;+attempts;+seconds</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: matchRules.leaderboards.weekly</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>["-cleared","+attempts","+seconds"]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Docs/export/current/04_che_do_kinh_te_ai.xlsx
+++ b/Docs/export/current/04_che_do_kinh_te_ai.xlsx
@@ -63,7 +63,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Meta_kinh_te_nguon'!$A$1:$I$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Meta_kinh_te_tran'!$A$1:$J$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Meta_kinh_te'!$A$1:$K$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Cai_dat_mac_dinh'!$A$1:$E$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Cai_dat_mac_dinh'!$A$1:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'Mutator_tuan'!$A$1:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Thu_hang'!$A$1:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Thuong'!$A$1:$E$2</definedName>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:422 (Rolls)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:479 (Rolls)</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:422 (Rolls)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:479 (Rolls)</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:422 (Rolls)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:479 (Rolls)</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:422 (Rolls)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:479 (Rolls)</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
@@ -11681,7 +11681,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:584 (Packs[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:641 (Packs[0])</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:584 (Packs[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:641 (Packs[1])</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:584 (Packs[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:641 (Packs[2])</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:585 (Packs[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:642 (Packs[3])</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:585 (Packs[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:642 (Packs[4])</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:585 (Packs[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:642 (Packs[5])</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -20062,12 +20062,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Game/Match/Arsenal.cs:564</t>
+          <t>Game/Match/Arsenal.cs:621</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>C#: Game/Match/Arsenal.cs:564</t>
+          <t>C#: Game/Match/Arsenal.cs:621</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -20099,12 +20099,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Game/Match/Arsenal.cs:563</t>
+          <t>Game/Match/Arsenal.cs:620</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C#: Game/Match/Arsenal.cs:563</t>
+          <t>C#: Game/Match/Arsenal.cs:620</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -21814,10 +21814,10 @@
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -21829,12 +21829,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>gia_tri</t>
+          <t>trang_thai</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>kieu</t>
+          <t>ghi_chu</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -21851,475 +21851,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aiHints</t>
-        </is>
-      </c>
-      <c r="B2" t="b">
-        <v>1</v>
+          <t>can_doc_ma</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>hằng mặc định trong GraphicsOptions.cs, Haptics.cs, PlayerProfile.cs; các mảng lựa chọn đồ họa ở Meta_bang_hang (GraphicsOptions#...)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>game.json balancePack.defaultSettings</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GraphicsOptions.cs</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>autoDeploy</t>
-        </is>
-      </c>
-      <c r="B3" t="b">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>autoStrike</t>
-        </is>
-      </c>
-      <c r="B4" t="b">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>batterySaver</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>brightness</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>100</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cameraSpeed</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cinematicMoments</t>
-        </is>
-      </c>
-      <c r="B8" t="b">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>colorBlind</t>
-        </is>
-      </c>
-      <c r="B9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>compactHud</t>
-        </is>
-      </c>
-      <c r="B10" t="b">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>dialogueVolume</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>effectsVolume</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>graphics</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>haptics</t>
-        </is>
-      </c>
-      <c r="B15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>musicVolume</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>screenShake</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>showCombatNumbers</t>
-        </is>
-      </c>
-      <c r="B19" t="b">
-        <v>0</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>showFps</t>
-        </is>
-      </c>
-      <c r="B20" t="b">
-        <v>0</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>textSize</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>uiSize</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>volume</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>game.json balancePack.defaultSettings</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E23"/>
+  <autoFilter ref="A1:E2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23553,8 +23106,10 @@
           <t>-bosses;+seconds;-parts</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -23578,8 +23133,10 @@
           <t>-bosses;+seconds;-parts</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>0.9</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -23603,8 +23160,10 @@
           <t>-waves;-killedBaseCp;-seconds</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>0.9</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -23628,8 +23187,10 @@
           <t>-waves;-killedBaseCp;-seconds</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>0.9</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -23653,8 +23214,10 @@
           <t>-waves;-killedBaseCp;-seconds</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>0.9</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -23678,8 +23241,10 @@
           <t>-cleared;+attempts;+seconds</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>0.9</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -27962,7 +27527,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>kill_share 0.25; tran_hoan_khi_ha 0.45; tran_hoan_khi_mat 0.15; duong_bat_kip (ban/doi_thu:tang_thu_nhap) 1:1;0.75:1;0.6:1.1364;0.5:1.2273;0.4:1.3182;0.3:1.4091;0.2:1.5;0.1:1.5; duong_phat_tiep_te (quan/tiep_te:thu_nhap_giu) 1:1;1.25:0.875;1.5:0.75;2:0.5;2.5:0.25;3:0.25</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -27990,7 +27555,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>armyCap = round((economy.armyCap[mode] x supplyPriceScale + bonus) x economy.supply x commander); supply = floor(armyCap x supplyPerArmyCap); income kept = max(upkeepFloor, 1 - upkeepSlope x (army - supply) / supply) above the supply</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">

--- a/Docs/export/current/04_che_do_kinh_te_ai.xlsx
+++ b/Docs/export/current/04_che_do_kinh_te_ai.xlsx
@@ -7678,7 +7678,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>780.5291475734409</v>
+        <v>801.409791010632</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -7755,7 +7755,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1561.058295146882</v>
+        <v>1602.819582021264</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -7832,7 +7832,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2341.587442720323</v>
+        <v>2404.229373031896</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3122.116590293764</v>
+        <v>3205.639164042528</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>57.525</v>
       </c>
       <c r="H18" t="n">
-        <v>119.7831510844486</v>
+        <v>134.2163644524049</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -8682,7 +8682,7 @@
         <v>243.375</v>
       </c>
       <c r="H19" t="n">
-        <v>119.7831510844486</v>
+        <v>134.2163644524049</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -8759,7 +8759,7 @@
         <v>433.65</v>
       </c>
       <c r="H20" t="n">
-        <v>119.7831510844486</v>
+        <v>134.2163644524049</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -8836,7 +8836,7 @@
         <v>818.6249999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>119.7831510844486</v>
+        <v>134.2163644524049</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>530.4682405168438</v>
+        <v>594.3867568606504</v>
       </c>
       <c r="J26" t="n">
         <v>53.95384615384615</v>
@@ -9301,7 +9301,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>530.4682405168438</v>
+        <v>594.3867568606504</v>
       </c>
       <c r="J27" t="n">
         <v>53.95384615384615</v>
@@ -9378,7 +9378,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>530.4682405168438</v>
+        <v>594.3867568606504</v>
       </c>
       <c r="J28" t="n">
         <v>53.95384615384615</v>
@@ -9455,7 +9455,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>530.4682405168438</v>
+        <v>594.3867568606504</v>
       </c>
       <c r="J29" t="n">
         <v>53.95384615384615</v>
@@ -9526,7 +9526,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>395.4012368521357</v>
+        <v>397.157261515015</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -9603,7 +9603,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1144.360818058753</v>
+        <v>1161.065332808506</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -9680,7 +9680,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1144.360818058753</v>
+        <v>1161.065332808506</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -9757,7 +9757,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>1144.360818058753</v>
+        <v>1161.065332808506</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -9840,7 +9840,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>530.4682405168438</v>
+        <v>594.3867568606504</v>
       </c>
       <c r="J34" t="n">
         <v>53.95384615384615</v>
@@ -9917,7 +9917,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>530.4682405168438</v>
+        <v>594.3867568606504</v>
       </c>
       <c r="J35" t="n">
         <v>53.95384615384615</v>
@@ -9994,7 +9994,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>530.4682405168438</v>
+        <v>594.3867568606504</v>
       </c>
       <c r="J36" t="n">
         <v>53.95384615384615</v>
@@ -10071,7 +10071,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>530.4682405168438</v>
+        <v>594.3867568606504</v>
       </c>
       <c r="J37" t="n">
         <v>53.95384615384615</v>

--- a/Docs/export/current/04_che_do_kinh_te_ai.xlsx
+++ b/Docs/export/current/04_che_do_kinh_te_ai.xlsx
@@ -7678,7 +7678,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>801.409791010632</v>
+        <v>799.0473871454815</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -7755,7 +7755,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1602.819582021264</v>
+        <v>1598.094774290963</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -7832,7 +7832,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2404.229373031896</v>
+        <v>2397.142161436444</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3205.639164042528</v>
+        <v>3196.189548581926</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -8602,10 +8602,10 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>57.525</v>
+        <v>59.9625</v>
       </c>
       <c r="H18" t="n">
-        <v>134.2163644524049</v>
+        <v>133.0011477705853</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -8679,10 +8679,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>243.375</v>
+        <v>253.6875</v>
       </c>
       <c r="H19" t="n">
-        <v>134.2163644524049</v>
+        <v>133.0011477705853</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -8756,10 +8756,10 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>433.65</v>
+        <v>452.025</v>
       </c>
       <c r="H20" t="n">
-        <v>134.2163644524049</v>
+        <v>133.0011477705853</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -8833,10 +8833,10 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>818.6249999999999</v>
+        <v>853.3124999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>134.2163644524049</v>
+        <v>133.0011477705853</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>594.3867568606504</v>
+        <v>589.0050829840205</v>
       </c>
       <c r="J26" t="n">
         <v>53.95384615384615</v>
@@ -9301,7 +9301,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>594.3867568606504</v>
+        <v>589.0050829840205</v>
       </c>
       <c r="J27" t="n">
         <v>53.95384615384615</v>
@@ -9378,7 +9378,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>594.3867568606504</v>
+        <v>589.0050829840205</v>
       </c>
       <c r="J28" t="n">
         <v>53.95384615384615</v>
@@ -9455,7 +9455,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>594.3867568606504</v>
+        <v>589.0050829840205</v>
       </c>
       <c r="J29" t="n">
         <v>53.95384615384615</v>
@@ -9526,7 +9526,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>397.157261515015</v>
+        <v>404.0082797189625</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -9603,7 +9603,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1161.065332808506</v>
+        <v>1181.206659716385</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -9680,7 +9680,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1161.065332808506</v>
+        <v>1181.206659716385</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -9757,7 +9757,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>1161.065332808506</v>
+        <v>1181.206659716385</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -9840,7 +9840,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>594.3867568606504</v>
+        <v>589.0050829840205</v>
       </c>
       <c r="J34" t="n">
         <v>53.95384615384615</v>
@@ -9917,7 +9917,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>594.3867568606504</v>
+        <v>589.0050829840205</v>
       </c>
       <c r="J35" t="n">
         <v>53.95384615384615</v>
@@ -9994,7 +9994,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>594.3867568606504</v>
+        <v>589.0050829840205</v>
       </c>
       <c r="J36" t="n">
         <v>53.95384615384615</v>
@@ -10071,7 +10071,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>594.3867568606504</v>
+        <v>589.0050829840205</v>
       </c>
       <c r="J37" t="n">
         <v>53.95384615384615</v>
